--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,58 +680,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102788778</v>
+        <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>99118</v>
+        <v>79140</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Olremmet, Hjd</t>
+          <t>Olremmet, Olremmet, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>469032</v>
+        <v>469316</v>
       </c>
       <c r="R2" t="n">
-        <v>6873233</v>
+        <v>6872944</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -755,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-08-05</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,13 +776,449 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136662728</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136662691</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93400</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Olremmet, Olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>469321</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6872931</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662691</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>102788778</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>469032</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6873233</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-08-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/102788778</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136662601</v>
+      </c>
+      <c r="B5" t="n">
+        <v>79232</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Olremmet, Olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>469208</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6872865</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662601</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136662562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>80064</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Olremmet, Olremmet, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>469188</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6872861</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136662562</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93400</v>
+        <v>93403</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93403</v>
+        <v>93404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79140</v>
+        <v>79142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93404</v>
+        <v>93409</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79232</v>
+        <v>79234</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80064</v>
+        <v>80066</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93409</v>
+        <v>93411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79142</v>
+        <v>79146</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93411</v>
+        <v>93413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79234</v>
+        <v>79238</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80066</v>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79146</v>
+        <v>79148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93413</v>
+        <v>93415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79238</v>
+        <v>79240</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80072</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79148</v>
+        <v>79149</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93415</v>
+        <v>93416</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79240</v>
+        <v>79241</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80072</v>
+        <v>80073</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93416</v>
+        <v>93422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79149</v>
+        <v>79151</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93422</v>
+        <v>93426</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79241</v>
+        <v>79243</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80073</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79151</v>
+        <v>79154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93426</v>
+        <v>93428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>79246</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80078</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79154</v>
+        <v>79167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93428</v>
+        <v>93441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79246</v>
+        <v>79259</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80078</v>
+        <v>80091</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136662728</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136662601</v>
       </c>
       <c r="B5" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>136662562</v>
       </c>
       <c r="B6" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -820,11 +820,7 @@
           <t>mycel</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Olremmet, Olremmet, Hjd</t>

--- a/artfynd/A 42773-2025 artfynd.xlsx
+++ b/artfynd/A 42773-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>136662691</v>
       </c>
       <c r="B3" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
